--- a/hourly datasets/cap_gen_year-5final.xlsx
+++ b/hourly datasets/cap_gen_year-5final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1283471711907002</v>
+        <v>0.1282432224656538</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09449192008675117</v>
+        <v>0.09629269173635838</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2228390912774513</v>
+        <v>0.2245359142020121</v>
       </c>
     </row>
     <row r="4">
@@ -513,25 +513,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1460624338489251</v>
+        <v>0.1516084967832159</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01323110543871133</v>
+        <v>0.01296501098378889</v>
       </c>
       <c r="D4" t="n">
-        <v>16.79724626981537</v>
+        <v>17.33987893731737</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06172975172326142</v>
+        <v>0.05750921045806163</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1201240062746966</v>
+        <v>0.126193592651568</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1720008614231536</v>
+        <v>0.1770234009148644</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2744096050396253</v>
+        <v>0.2798517192488696</v>
       </c>
     </row>
     <row r="5">
@@ -541,25 +541,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1724680637246444</v>
+        <v>0.1783257488671618</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01384975000143224</v>
+        <v>0.01355187350313673</v>
       </c>
       <c r="D5" t="n">
-        <v>20.16425648471064</v>
+        <v>20.78665932317764</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02873168118109861</v>
+        <v>0.01587053643361754</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1453168840976969</v>
+        <v>0.1517606424462842</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1996192433515918</v>
+        <v>0.2048908552880385</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3008152349153446</v>
+        <v>0.3065689713328156</v>
       </c>
     </row>
     <row r="6">
@@ -569,25 +569,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0434377670228085</v>
+        <v>0.04435423209416304</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007209298233841636</v>
+        <v>0.006624888224057027</v>
       </c>
       <c r="D6" t="n">
-        <v>4.055302242545266</v>
+        <v>4.110852218586184</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04005911692821068</v>
+        <v>0.0168640778577235</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02930339605294511</v>
+        <v>0.03136774800196449</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05757213799267171</v>
+        <v>0.05734071618636165</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1717849382135087</v>
+        <v>0.1725974545598168</v>
       </c>
     </row>
     <row r="7">
@@ -597,25 +597,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01015070786269167</v>
+        <v>0.01032011767746351</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009367810683311316</v>
+        <v>0.008800555681709298</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5258282562241506</v>
+        <v>0.5211631734177777</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06439913126973061</v>
+        <v>0.03892128362999427</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.00821508971853884</v>
+        <v>-0.006931157944083185</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02851650544392218</v>
+        <v>0.02757139329901032</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1384978790533918</v>
+        <v>0.1385633401431173</v>
       </c>
     </row>
     <row r="8">
@@ -625,25 +625,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00161840244930126</v>
+        <v>0.003905020828476456</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001747973746226867</v>
+        <v>0.0002046026507301494</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1271266379842217</v>
+        <v>0.2766068990727341</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05077036466357928</v>
+        <v>6.018435799284982e-80</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.001813190022051884</v>
+        <v>0.003503897506358146</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005049994920654397</v>
+        <v>0.004306144150594778</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1299655736400014</v>
+        <v>0.1321482432941302</v>
       </c>
     </row>
     <row r="9">
@@ -653,25 +653,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001682823578696667</v>
+        <v>0.003987068895523784</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001803103255346178</v>
+        <v>0.0002527182893687591</v>
       </c>
       <c r="D9" t="n">
-        <v>0.103707750902776</v>
+        <v>0.2286482997563658</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05162131332345483</v>
+        <v>1.94374125044361e-56</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.001856937422826739</v>
+        <v>0.003491614904923469</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005222584580220077</v>
+        <v>0.004482522886124088</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1300299947693968</v>
+        <v>0.1322302913611775</v>
       </c>
     </row>
     <row r="10">
@@ -681,25 +681,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001692767392222611</v>
+        <v>0.004192760924084501</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001701322642795205</v>
+        <v>0.000240652432882419</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1113599791684331</v>
+        <v>0.2524996333753151</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04811252729149144</v>
+        <v>1.201347547950533e-67</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.001647179855757642</v>
+        <v>0.003720962034826874</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005032714640202895</v>
+        <v>0.004664559813342128</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1300399385829228</v>
+        <v>0.1324359833897382</v>
       </c>
     </row>
     <row r="11">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03147538891119178</v>
+        <v>0.03184268280309725</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -717,7 +717,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1598225601018919</v>
+        <v>0.160085905268751</v>
       </c>
     </row>
     <row r="12">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03922476726033438</v>
+        <v>0.04039978325979061</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -735,7 +735,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1675719384510345</v>
+        <v>0.1686430057254444</v>
       </c>
     </row>
     <row r="13">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04784333304267697</v>
+        <v>0.04748683602954312</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -753,7 +753,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1761905042333771</v>
+        <v>0.1757300584951969</v>
       </c>
     </row>
     <row r="14">
@@ -763,25 +763,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05651374122956527</v>
+        <v>0.05575316962940188</v>
       </c>
       <c r="C14" t="n">
-        <v>0.009238705980531569</v>
+        <v>0.008933022056064865</v>
       </c>
       <c r="D14" t="n">
-        <v>8.300778374843642</v>
+        <v>8.163536466617925</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05356358624673146</v>
+        <v>0.04900877331451291</v>
       </c>
       <c r="F14" t="n">
-        <v>0.03840220760769205</v>
+        <v>0.03824172513083005</v>
       </c>
       <c r="G14" t="n">
-        <v>0.07462527485143847</v>
+        <v>0.07326461412797368</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1848609124202654</v>
+        <v>0.1839963920950556</v>
       </c>
     </row>
     <row r="15">
@@ -791,25 +791,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05783578934588145</v>
+        <v>0.05926434782110192</v>
       </c>
       <c r="C15" t="n">
-        <v>0.008968095987557463</v>
+        <v>0.00874242917210967</v>
       </c>
       <c r="D15" t="n">
-        <v>9.267222408083235</v>
+        <v>9.208349749742482</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05228423006023787</v>
+        <v>0.0519998392553107</v>
       </c>
       <c r="F15" t="n">
-        <v>0.04025488389112222</v>
+        <v>0.0421265150673696</v>
       </c>
       <c r="G15" t="n">
-        <v>0.07541669480064073</v>
+        <v>0.07640218057483428</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1861829605365816</v>
+        <v>0.1875075702867557</v>
       </c>
     </row>
     <row r="16">
@@ -819,25 +819,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06410734882481585</v>
+        <v>0.06287459725978854</v>
       </c>
       <c r="C16" t="n">
-        <v>0.008798491287097924</v>
+        <v>0.008680698759609072</v>
       </c>
       <c r="D16" t="n">
-        <v>9.492926164133314</v>
+        <v>9.33791601160323</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03825106689739993</v>
+        <v>0.0368869278505935</v>
       </c>
       <c r="F16" t="n">
-        <v>0.04685962590760655</v>
+        <v>0.04585773806727389</v>
       </c>
       <c r="G16" t="n">
-        <v>0.08135507174202508</v>
+        <v>0.07989145645230311</v>
       </c>
       <c r="H16" t="n">
-        <v>0.192454520015516</v>
+        <v>0.1911178197254423</v>
       </c>
     </row>
     <row r="17">
@@ -847,25 +847,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06651823234722766</v>
+        <v>0.06573997265550063</v>
       </c>
       <c r="C17" t="n">
-        <v>0.008956241903316169</v>
+        <v>0.008622433400812892</v>
       </c>
       <c r="D17" t="n">
-        <v>10.26564344497893</v>
+        <v>10.11784478971471</v>
       </c>
       <c r="E17" t="n">
-        <v>0.05977553374702421</v>
+        <v>0.05185772214131067</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04896042422358238</v>
+        <v>0.04883742132629446</v>
       </c>
       <c r="G17" t="n">
-        <v>0.08407604047087301</v>
+        <v>0.08264252398470685</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1948654035379278</v>
+        <v>0.1939831951211544</v>
       </c>
     </row>
     <row r="18">
@@ -875,22 +875,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1283471711907002</v>
+        <v>-0.1282432224656538</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0146469865159258</v>
+        <v>0.01478621307297395</v>
       </c>
       <c r="D18" t="n">
-        <v>-16.76406377529664</v>
+        <v>-16.77069674149833</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03585037240326046</v>
+        <v>0.0348596619839967</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1570596087897323</v>
+        <v>-0.1572286876099879</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.09963473359166772</v>
+        <v>-0.09925775732131928</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -903,25 +903,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06800771052348256</v>
+        <v>0.06571311887438624</v>
       </c>
       <c r="C19" t="n">
-        <v>0.008825492094854425</v>
+        <v>0.008752765717431827</v>
       </c>
       <c r="D19" t="n">
-        <v>10.45182833363226</v>
+        <v>10.02969240322329</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04428145680998403</v>
+        <v>0.0452104649416136</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0507071708215549</v>
+        <v>0.04855513837221812</v>
       </c>
       <c r="G19" t="n">
-        <v>0.08530825022541025</v>
+        <v>0.08287109937655439</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1963548817141827</v>
+        <v>0.19395634134004</v>
       </c>
     </row>
     <row r="20">
@@ -931,25 +931,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.06579559924731158</v>
+        <v>0.06539514282780619</v>
       </c>
       <c r="C20" t="n">
-        <v>0.009428708209947607</v>
+        <v>0.009136441906477097</v>
       </c>
       <c r="D20" t="n">
-        <v>9.697279918385963</v>
+        <v>9.353149124932029</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04679189595954047</v>
+        <v>0.04603628226696484</v>
       </c>
       <c r="F20" t="n">
-        <v>0.04731157480573898</v>
+        <v>0.04748510182564546</v>
       </c>
       <c r="G20" t="n">
-        <v>0.08427962368888425</v>
+        <v>0.08330518382996698</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1941427704380118</v>
+        <v>0.19363836529346</v>
       </c>
     </row>
     <row r="21">
@@ -959,25 +959,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0678054141321454</v>
+        <v>0.06613027219997071</v>
       </c>
       <c r="C21" t="n">
-        <v>0.009562425714968336</v>
+        <v>0.009349076720267867</v>
       </c>
       <c r="D21" t="n">
-        <v>9.899177679775631</v>
+        <v>9.526285552524003</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05299972288932873</v>
+        <v>0.05038267903251423</v>
       </c>
       <c r="F21" t="n">
-        <v>0.04905950269070068</v>
+        <v>0.04780338542511086</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08655132557359005</v>
+        <v>0.08445715897483048</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1961525853228456</v>
+        <v>0.1943734946656245</v>
       </c>
     </row>
     <row r="22">
@@ -987,25 +987,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.07012762568867303</v>
+        <v>0.06877529087176096</v>
       </c>
       <c r="C22" t="n">
-        <v>0.009507764203008078</v>
+        <v>0.00932134624088693</v>
       </c>
       <c r="D22" t="n">
-        <v>10.31332800466905</v>
+        <v>9.951209240437869</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04596065446455883</v>
+        <v>0.04616268703637391</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0514889202494399</v>
+        <v>0.05050276831269523</v>
       </c>
       <c r="G22" t="n">
-        <v>0.08876633112790615</v>
+        <v>0.08704781343082664</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1984747968793732</v>
+        <v>0.1970185133374147</v>
       </c>
     </row>
     <row r="23">
@@ -1015,25 +1015,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.07218723260172487</v>
+        <v>0.07074198220372677</v>
       </c>
       <c r="C23" t="n">
-        <v>0.009696192544541805</v>
+        <v>0.00945822960694191</v>
       </c>
       <c r="D23" t="n">
-        <v>9.95552957726091</v>
+        <v>9.6014753598519</v>
       </c>
       <c r="E23" t="n">
-        <v>0.05508957454943995</v>
+        <v>0.05641813692386864</v>
       </c>
       <c r="F23" t="n">
-        <v>0.05317905962313235</v>
+        <v>0.0522011453022486</v>
       </c>
       <c r="G23" t="n">
-        <v>0.09119540558031736</v>
+        <v>0.08928281910520484</v>
       </c>
       <c r="H23" t="n">
-        <v>0.200534403792425</v>
+        <v>0.1989852046693805</v>
       </c>
     </row>
     <row r="24">
@@ -1043,25 +1043,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.07486459884528214</v>
+        <v>0.07355297399639651</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0101176470140074</v>
+        <v>0.009942490313963017</v>
       </c>
       <c r="D24" t="n">
-        <v>10.39028584542346</v>
+        <v>10.09781310423222</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06818537152253543</v>
+        <v>0.06246184269528575</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05503021951344969</v>
+        <v>0.05406283960580583</v>
       </c>
       <c r="G24" t="n">
-        <v>0.09469897817711447</v>
+        <v>0.09304310838698714</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2032117700359823</v>
+        <v>0.2017961964620503</v>
       </c>
     </row>
     <row r="25">
@@ -1071,25 +1071,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.08300676007699219</v>
+        <v>0.0813772083713704</v>
       </c>
       <c r="C25" t="n">
-        <v>0.01043801347261542</v>
+        <v>0.0102527768899124</v>
       </c>
       <c r="D25" t="n">
-        <v>11.39838693396223</v>
+        <v>11.09819421691112</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05690338991671311</v>
+        <v>0.05707244826795769</v>
       </c>
       <c r="F25" t="n">
-        <v>0.06254440571954402</v>
+        <v>0.06127882517697763</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1034691144344403</v>
+        <v>0.1014755915657631</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2113539312676924</v>
+        <v>0.2096204308370241</v>
       </c>
     </row>
     <row r="26">
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.08685996637668637</v>
+        <v>0.0853692819097351</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01050362606776458</v>
+        <v>0.01028715814626273</v>
       </c>
       <c r="D26" t="n">
-        <v>11.84474282479547</v>
+        <v>11.6615138862764</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06665017955462341</v>
+        <v>0.06603264040290353</v>
       </c>
       <c r="F26" t="n">
-        <v>0.06626890866842584</v>
+        <v>0.06520352859809203</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1074510240849467</v>
+        <v>0.1055350352213781</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2152071375673865</v>
+        <v>0.2136125043753889</v>
       </c>
     </row>
     <row r="27">
@@ -1127,25 +1127,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.08193508997604323</v>
+        <v>0.08310460461811373</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01061094176786122</v>
+        <v>0.01038274908266457</v>
       </c>
       <c r="D27" t="n">
-        <v>10.06884644387057</v>
+        <v>10.16852938037038</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07429421224318587</v>
+        <v>0.07546098297002507</v>
       </c>
       <c r="F27" t="n">
-        <v>0.06113365236423705</v>
+        <v>0.06275155090918437</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1027365275878495</v>
+        <v>0.1034576583270431</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2102822611667434</v>
+        <v>0.2113478270837675</v>
       </c>
     </row>
     <row r="28">
@@ -1155,25 +1155,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.08133877163213249</v>
+        <v>0.08356781870395109</v>
       </c>
       <c r="C28" t="n">
-        <v>0.01153018993159845</v>
+        <v>0.01131816368380187</v>
       </c>
       <c r="D28" t="n">
-        <v>9.39399048153704</v>
+        <v>9.670352094265747</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1179438253289816</v>
+        <v>0.1035477869546741</v>
       </c>
       <c r="F28" t="n">
-        <v>0.05873502484228068</v>
+        <v>0.06138094284444894</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1039425184219842</v>
+        <v>0.1057546945634531</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2096859428228326</v>
+        <v>0.2118110411696049</v>
       </c>
     </row>
     <row r="29">
@@ -1183,25 +1183,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.001749785190761427</v>
+        <v>0.004172768424209374</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001648375808876918</v>
+        <v>0.0001807014368030567</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1557838948624331</v>
+        <v>0.3346675365099462</v>
       </c>
       <c r="E29" t="n">
-        <v>0.04998096453408336</v>
+        <v>2.407651611882518e-113</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.001486296159514917</v>
+        <v>0.0038185034115943</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004985866541037763</v>
+        <v>0.004527033436824459</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1300969563814616</v>
+        <v>0.1324159908898631</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year-5final.xlsx
+++ b/hourly datasets/cap_gen_year-5final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2422552969829816</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1282432224656538</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1253800697401367</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09629269173635838</v>
+        <v>0.3145613561870834</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2245359142020121</v>
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1976861289442385</v>
       </c>
     </row>
     <row r="4">
@@ -513,25 +524,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1516084967832159</v>
+        <v>0.2862983427215751</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01296501098378889</v>
+        <v>0.01153090664627845</v>
       </c>
       <c r="D4" t="n">
-        <v>17.33987893731737</v>
+        <v>14.17253785214039</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05750921045806163</v>
+        <v>0.05647603231608045</v>
       </c>
       <c r="F4" t="n">
-        <v>0.126193592651568</v>
+        <v>0.1007651624239761</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1770234009148644</v>
+        <v>0.1459724747933556</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2798517192488696</v>
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1694231154787302</v>
       </c>
     </row>
     <row r="5">
@@ -541,25 +555,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1783257488671618</v>
+        <v>0.340230792926699</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01355187350313673</v>
+        <v>0.01364044783975854</v>
       </c>
       <c r="D5" t="n">
-        <v>20.78665932317764</v>
+        <v>20.92251984162978</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01587053643361754</v>
+        <v>0.01597426542991569</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1517606424462842</v>
+        <v>0.1527525420701162</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2048908552880385</v>
+        <v>0.2062300112049538</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3065689713328156</v>
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2233555656838541</v>
       </c>
     </row>
     <row r="6">
@@ -569,25 +586,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04435423209416304</v>
+        <v>0.293848008898297</v>
       </c>
       <c r="C6" t="n">
-        <v>0.006624888224057027</v>
+        <v>0.01640374795129282</v>
       </c>
       <c r="D6" t="n">
-        <v>4.110852218586184</v>
+        <v>14.16592279786266</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0168640778577235</v>
+        <v>0.02592907364444392</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03136774800196449</v>
+        <v>0.1326141455778764</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05734071618636165</v>
+        <v>0.1969253507926721</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1725974545598168</v>
+        <v>13</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1769727816554522</v>
       </c>
     </row>
     <row r="7">
@@ -597,25 +617,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01032011767746351</v>
+        <v>0.313209288634004</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008800555681709298</v>
+        <v>0.1157139207468763</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5211631734177777</v>
+        <v>1.598941972261994</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03892128362999427</v>
+        <v>0.5407598891089207</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.006931157944083185</v>
+        <v>-0.1521930422199295</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02757139329901032</v>
+        <v>0.3014611537896633</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1385633401431173</v>
+        <v>30</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1963340613911591</v>
       </c>
     </row>
     <row r="8">
@@ -625,25 +648,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003905020828476456</v>
+        <v>0.4961855959799183</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0002046026507301494</v>
+        <v>0.01494802895334387</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2766068990727341</v>
+        <v>20.20857462637271</v>
       </c>
       <c r="E8" t="n">
-        <v>6.018435799284982e-80</v>
+        <v>4.396998389830562e-78</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003503897506358146</v>
+        <v>0.2559906295821657</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004306144150594778</v>
+        <v>0.3146018255905123</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1321482432941302</v>
+        <v>138</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.3793103687370734</v>
       </c>
     </row>
     <row r="9">
@@ -653,25 +679,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003987068895523784</v>
+        <v>0.5021799312312577</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0002527182893687591</v>
+        <v>0.018463300905647</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2286482997563658</v>
+        <v>16.70477578220037</v>
       </c>
       <c r="E9" t="n">
-        <v>1.94374125044361e-56</v>
+        <v>1.42007449002998e-54</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003491614904923469</v>
+        <v>0.2550932771714677</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004482522886124088</v>
+        <v>0.3274878485038895</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1322302913611775</v>
+        <v>138</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.3853047039884128</v>
       </c>
     </row>
     <row r="10">
@@ -681,25 +710,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.004192760924084501</v>
+        <v>0.517207548847282</v>
       </c>
       <c r="C10" t="n">
-        <v>0.000240652432882419</v>
+        <v>0.01758178362588026</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2524996333753151</v>
+        <v>18.44732615600832</v>
       </c>
       <c r="E10" t="n">
-        <v>1.201347547950533e-67</v>
+        <v>8.776903850320953e-66</v>
       </c>
       <c r="F10" t="n">
-        <v>0.003720962034826874</v>
+        <v>0.2718491086620577</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004664559813342128</v>
+        <v>0.3407872522453484</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1324359833897382</v>
+        <v>138</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.4003323216044372</v>
       </c>
     </row>
     <row r="11">
@@ -709,7 +741,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03184268280309725</v>
+        <v>0.2846625319333782</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -717,7 +749,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.160085905268751</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1677873046905333</v>
       </c>
     </row>
     <row r="12">
@@ -727,7 +762,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04039978325979061</v>
+        <v>0.2963646942557381</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -735,7 +770,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1686430057254444</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1794894670128933</v>
       </c>
     </row>
     <row r="13">
@@ -745,7 +783,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04748683602954312</v>
+        <v>0.3086240115132508</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -753,7 +791,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1757300584951969</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1917487842704059</v>
       </c>
     </row>
     <row r="14">
@@ -763,25 +804,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05575316962940188</v>
+        <v>0.3148852914518067</v>
       </c>
       <c r="C14" t="n">
-        <v>0.008933022056064865</v>
+        <v>0.008921921171025488</v>
       </c>
       <c r="D14" t="n">
-        <v>8.163536466617925</v>
+        <v>8.156427251920739</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04900877331451291</v>
+        <v>0.04897625468765551</v>
       </c>
       <c r="F14" t="n">
-        <v>0.03824172513083005</v>
+        <v>0.03818943605274035</v>
       </c>
       <c r="G14" t="n">
-        <v>0.07326461412797368</v>
+        <v>0.07316880286757928</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1839963920950556</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1980100642089618</v>
       </c>
     </row>
     <row r="15">
@@ -791,25 +835,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05926434782110192</v>
+        <v>0.318230412532292</v>
       </c>
       <c r="C15" t="n">
-        <v>0.00874242917210967</v>
+        <v>0.008727606321258689</v>
       </c>
       <c r="D15" t="n">
-        <v>9.208349749742482</v>
+        <v>9.193648239363664</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0519998392553107</v>
+        <v>0.05182992854584995</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0421265150673696</v>
+        <v>0.04203242429317612</v>
       </c>
       <c r="G15" t="n">
-        <v>0.07640218057483428</v>
+        <v>0.07624997473159449</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1875075702867557</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2013551852894471</v>
       </c>
     </row>
     <row r="16">
@@ -819,25 +866,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06287459725978854</v>
+        <v>0.3217424352983251</v>
       </c>
       <c r="C16" t="n">
-        <v>0.008680698759609072</v>
+        <v>0.008665667590427814</v>
       </c>
       <c r="D16" t="n">
-        <v>9.33791601160323</v>
+        <v>9.318150138561402</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0368869278505935</v>
+        <v>0.03655012454385226</v>
       </c>
       <c r="F16" t="n">
-        <v>0.04585773806727389</v>
+        <v>0.04573969036256365</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07989145645230311</v>
+        <v>0.07971447689618569</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1911178197254423</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2048672080554803</v>
       </c>
     </row>
     <row r="17">
@@ -847,25 +897,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06573997265550063</v>
+        <v>0.3240912752004788</v>
       </c>
       <c r="C17" t="n">
-        <v>0.008622433400812892</v>
+        <v>0.008601672157894211</v>
       </c>
       <c r="D17" t="n">
-        <v>10.11784478971471</v>
+        <v>10.09152895334447</v>
       </c>
       <c r="E17" t="n">
-        <v>0.05185772214131067</v>
+        <v>0.05159301349036</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04883742132629446</v>
+        <v>0.04867594300842393</v>
       </c>
       <c r="G17" t="n">
-        <v>0.08264252398470685</v>
+        <v>0.08239964868687033</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1939831951211544</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2072160479576339</v>
       </c>
     </row>
     <row r="18">
@@ -875,24 +928,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1282432224656538</v>
+        <v>0.1168752272428449</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01478621307297395</v>
+        <v>0.01468944144010225</v>
       </c>
       <c r="D18" t="n">
-        <v>-16.77069674149833</v>
+        <v>-16.67278070883062</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0348596619839967</v>
+        <v>0.03476709161662294</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1572286876099879</v>
+        <v>-0.156201929102407</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.09925775732131928</v>
+        <v>-0.09861040384999321</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -903,25 +959,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06571311887438624</v>
+        <v>0.32492994165991</v>
       </c>
       <c r="C19" t="n">
-        <v>0.008752765717431827</v>
+        <v>0.008724257237777044</v>
       </c>
       <c r="D19" t="n">
-        <v>10.02969240322329</v>
+        <v>9.996074021212941</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0452104649416136</v>
+        <v>0.04500549787514681</v>
       </c>
       <c r="F19" t="n">
-        <v>0.04855513837221812</v>
+        <v>0.04834501572856204</v>
       </c>
       <c r="G19" t="n">
-        <v>0.08287109937655439</v>
+        <v>0.08254920626770432</v>
       </c>
       <c r="H19" t="n">
-        <v>0.19395634134004</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2080547144170651</v>
       </c>
     </row>
     <row r="20">
@@ -931,25 +990,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.06539514282780619</v>
+        <v>0.3263837145832078</v>
       </c>
       <c r="C20" t="n">
-        <v>0.009136441906477097</v>
+        <v>0.009097595836915091</v>
       </c>
       <c r="D20" t="n">
-        <v>9.353149124932029</v>
+        <v>9.315494925877379</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04603628226696484</v>
+        <v>0.04570671150672168</v>
       </c>
       <c r="F20" t="n">
-        <v>0.04748510182564546</v>
+        <v>0.04724996575817743</v>
       </c>
       <c r="G20" t="n">
-        <v>0.08330518382996698</v>
+        <v>0.08291774773092904</v>
       </c>
       <c r="H20" t="n">
-        <v>0.19363836529346</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2095084873403629</v>
       </c>
     </row>
     <row r="21">
@@ -959,25 +1021,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.06613027219997071</v>
+        <v>0.3252091815446558</v>
       </c>
       <c r="C21" t="n">
-        <v>0.009349076720267867</v>
+        <v>0.009292860428140884</v>
       </c>
       <c r="D21" t="n">
-        <v>9.526285552524003</v>
+        <v>9.474248067983826</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05038267903251423</v>
+        <v>0.05009674422626391</v>
       </c>
       <c r="F21" t="n">
-        <v>0.04780338542511086</v>
+        <v>0.04749002176490532</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08445715897483048</v>
+        <v>0.08392339299793816</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1943734946656245</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.208333954301811</v>
       </c>
     </row>
     <row r="22">
@@ -987,25 +1052,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.06877529087176096</v>
+        <v>0.32564837861984</v>
       </c>
       <c r="C22" t="n">
-        <v>0.00932134624088693</v>
+        <v>0.009248889858243131</v>
       </c>
       <c r="D22" t="n">
-        <v>9.951209240437869</v>
+        <v>9.862203303747226</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04616268703637391</v>
+        <v>0.04570848662237343</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05050276831269523</v>
+        <v>0.04998056004458946</v>
       </c>
       <c r="G22" t="n">
-        <v>0.08704781343082664</v>
+        <v>0.08624153183486559</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1970185133374147</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2087731513769951</v>
       </c>
     </row>
     <row r="23">
@@ -1015,25 +1083,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.07074198220372677</v>
+        <v>0.3242557738547276</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00945822960694191</v>
+        <v>0.009364883744234951</v>
       </c>
       <c r="D23" t="n">
-        <v>9.6014753598519</v>
+        <v>9.484981635615897</v>
       </c>
       <c r="E23" t="n">
-        <v>0.05641813692386864</v>
+        <v>0.05554005138260142</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0522011453022486</v>
+        <v>0.05150930810437751</v>
       </c>
       <c r="G23" t="n">
-        <v>0.08928281910520484</v>
+        <v>0.08822500889842511</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1989852046693805</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2073805466118827</v>
       </c>
     </row>
     <row r="24">
@@ -1043,25 +1114,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.07355297399639651</v>
+        <v>0.3263565755623398</v>
       </c>
       <c r="C24" t="n">
-        <v>0.009942490313963017</v>
+        <v>0.009821387821166764</v>
       </c>
       <c r="D24" t="n">
-        <v>10.09781310423222</v>
+        <v>9.954286546777311</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06246184269528575</v>
+        <v>0.06149551825494849</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05406283960580583</v>
+        <v>0.05322192684861963</v>
       </c>
       <c r="G24" t="n">
-        <v>0.09304310838698714</v>
+        <v>0.09172739877887838</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2017961964620503</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2094813483194949</v>
       </c>
     </row>
     <row r="25">
@@ -1071,25 +1145,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0813772083713704</v>
+        <v>0.3273807104656135</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0102527768899124</v>
+        <v>0.01005451050836413</v>
       </c>
       <c r="D25" t="n">
-        <v>11.09819421691112</v>
+        <v>10.77257947938217</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05707244826795769</v>
+        <v>0.05617011466721366</v>
       </c>
       <c r="F25" t="n">
-        <v>0.06127882517697763</v>
+        <v>0.0589216132263221</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1014755915657631</v>
+        <v>0.09834105718827589</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2096204308370241</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2105054832227686</v>
       </c>
     </row>
     <row r="26">
@@ -1099,25 +1176,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0853692819097351</v>
+        <v>0.3287809805955695</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01028715814626273</v>
+        <v>0.01004642608701583</v>
       </c>
       <c r="D26" t="n">
-        <v>11.6615138862764</v>
+        <v>11.25689372132714</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06603264040290353</v>
+        <v>0.06503673401459453</v>
       </c>
       <c r="F26" t="n">
-        <v>0.06520352859809203</v>
+        <v>0.06217802059203726</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1055350352213781</v>
+        <v>0.1015657140650964</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2136125043753889</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2119057533527247</v>
       </c>
     </row>
     <row r="27">
@@ -1127,25 +1207,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.08310460461811373</v>
+        <v>0.3283053907823258</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01038274908266457</v>
+        <v>0.01011883650830428</v>
       </c>
       <c r="D27" t="n">
-        <v>10.16852938037038</v>
+        <v>9.726881858931561</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07546098297002507</v>
+        <v>0.07428201915323424</v>
       </c>
       <c r="F27" t="n">
-        <v>0.06275155090918437</v>
+        <v>0.0594502700081327</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1034576583270431</v>
+        <v>0.09912168421114947</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2113478270837675</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.211430163539481</v>
       </c>
     </row>
     <row r="28">
@@ -1155,25 +1238,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.08356781870395109</v>
+        <v>0.327270833179958</v>
       </c>
       <c r="C28" t="n">
-        <v>0.01131816368380187</v>
+        <v>0.01099583007525181</v>
       </c>
       <c r="D28" t="n">
-        <v>9.670352094265747</v>
+        <v>9.198701545541239</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1035477869546741</v>
+        <v>0.1015981777485648</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06138094284444894</v>
+        <v>0.05785495837678091</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1057546945634531</v>
+        <v>0.1009649588753142</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2118110411696049</v>
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2103956059371132</v>
       </c>
     </row>
     <row r="29">
@@ -1183,25 +1269,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.004172768424209374</v>
+        <v>0.5157469203269939</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0001807014368030567</v>
+        <v>0.01320183438290567</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3346675365099462</v>
+        <v>24.45041649090313</v>
       </c>
       <c r="E29" t="n">
-        <v>2.407651611882518e-113</v>
+        <v>1.759001942328288e-111</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0038185034115943</v>
+        <v>0.2789753668941249</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004527033436824459</v>
+        <v>0.3307397369727045</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1324159908898631</v>
+        <v>138</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.398871693084149</v>
       </c>
     </row>
   </sheetData>
